--- a/m4_peripheral_record.xlsx
+++ b/m4_peripheral_record.xlsx
@@ -8,14 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\02_git\02_development\pac2514x_example_code\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{53888694-77AA-4D10-B5D6-569AED0C30B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F0D58A60-A010-494F-A14C-12B864B944D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="uart" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId2"/>
+    <sheet name="system_clock" sheetId="2" r:id="rId3"/>
+    <sheet name="flash" sheetId="3" r:id="rId4"/>
   </sheets>
   <calcPr calcId="162913"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -25,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="7">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>configuration step</t>
   </si>
@@ -46,6 +50,30 @@
   </si>
   <si>
     <t xml:space="preserve">configure GPIO  </t>
+  </si>
+  <si>
+    <t>FRCLK</t>
+  </si>
+  <si>
+    <t>PLLCLK</t>
+  </si>
+  <si>
+    <t>SCLK</t>
+  </si>
+  <si>
+    <t>HCLK</t>
+  </si>
+  <si>
+    <t>PCLK</t>
+  </si>
+  <si>
+    <t>ACLK</t>
+  </si>
+  <si>
+    <t>MCLK of flash should be configured to 30MHz otherwise you can`t write flash</t>
+  </si>
+  <si>
+    <t>KGU VB6 floating</t>
   </si>
 </sst>
 </file>
@@ -185,6 +213,285 @@
         <a:xfrm>
           <a:off x="8135324" y="5848350"/>
           <a:ext cx="7224394" cy="3810000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>95250</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>445745</xdr:colOff>
+      <xdr:row>43</xdr:row>
+      <xdr:rowOff>48940</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{234F655E-1B8D-DC6B-B60F-DBD4DDC1C596}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1314450" y="781050"/>
+          <a:ext cx="8884895" cy="7459390"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>104774</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>38099</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>579547</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A19A9312-9E4E-939E-0C14-8300BB1B534E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="9248774" y="419099"/>
+          <a:ext cx="9618773" cy="6010276"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing4.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>409576</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>28574</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>225138</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>163265</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2072043F-9424-708F-BA91-0C20A99F0200}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="7724776" y="790574"/>
+          <a:ext cx="5911562" cy="6992691"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>23</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>112371</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>35</xdr:col>
+      <xdr:colOff>115817</xdr:colOff>
+      <xdr:row>37</xdr:row>
+      <xdr:rowOff>106058</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Picture 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2DE746BF-1465-2CE7-2EDB-AAB057F11C9D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="14258925" y="1064871"/>
+          <a:ext cx="7192892" cy="6089687"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>285750</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>30</xdr:col>
+      <xdr:colOff>182322</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>181080</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Picture 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F2633F47-7C5F-C67E-D0F7-34FD960F6CC9}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8820150" y="7810500"/>
+          <a:ext cx="9650172" cy="752580"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>400049</xdr:colOff>
+      <xdr:row>45</xdr:row>
+      <xdr:rowOff>73047</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>28</xdr:col>
+      <xdr:colOff>487212</xdr:colOff>
+      <xdr:row>63</xdr:row>
+      <xdr:rowOff>86298</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Picture 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{82DAACD9-F86E-433B-6EA8-72435667D9A1}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="8934449" y="8645547"/>
+          <a:ext cx="8621563" cy="3442251"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -521,6 +828,72 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2EEF5E26-673A-45A9-AE8E-707F9F247085}">
+  <dimension ref="C4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="4" spans="3:3" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D6EB2149-4C37-4F43-B0BA-D470A01FE0AD}">
+  <dimension ref="C4:H4"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="3" max="3" width="12.42578125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="3:8" x14ac:dyDescent="0.25">
+      <c r="C4" t="s">
+        <v>7</v>
+      </c>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" t="s">
+        <v>11</v>
+      </c>
+      <c r="H4" t="s">
+        <v>12</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB01F81-A64C-4F3E-9A98-62321CD5550A}">
+  <dimension ref="B8"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetData>
+    <row r="8" spans="2:2" x14ac:dyDescent="0.25">
+      <c r="B8" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
 <file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
 <clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
   <clbl:label id="{783439ab-34c5-49cd-8f76-f98ee7c0bf70}" enabled="1" method="Privileged" siteId="{ea529389-cf47-4fb2-b8ff-2ddd0b7d2a34}" contentBits="2" removed="0"/>
